--- a/Base_de_datos.xlsx
+++ b/Base_de_datos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="15" documentId="11_042DB46D7C8895CFC4CE9A4A2A8BD4CC64FBD28F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B4A9AC4-488B-4D62-B745-E0182E29EC07}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4815" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transacciones_fact" sheetId="1" r:id="rId1"/>
